--- a/storage/templates/constancia_traslado.xlsx
+++ b/storage/templates/constancia_traslado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sistema_hospital\storage\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADC59EE-C6DF-4E01-8BCF-3EFE5AE78A0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B31E1C57-B9BB-43DA-8FE7-5715875A677E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="918" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,7 +97,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,7 +167,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -366,105 +373,105 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -826,21 +833,21 @@
     </row>
     <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
@@ -852,31 +859,31 @@
       <c r="E5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="36" t="s">
+      <c r="F5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="33"/>
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" ht="18" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:7" s="4" customFormat="1" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38" t="s">
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="38"/>
+      <c r="G7" s="35"/>
     </row>
     <row r="8" spans="1:7" s="5" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="20" t="s">
         <v>16</v>
       </c>
@@ -897,11 +904,11 @@
       <c r="A10" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="38"/>
       <c r="E10" s="16" t="s">
         <v>7</v>
       </c>
@@ -913,103 +920,103 @@
       </c>
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="54"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="39"/>
     </row>
     <row r="12" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
-      <c r="B12" s="48"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="54"/>
+      <c r="A12" s="39"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="54"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="39"/>
     </row>
     <row r="14" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
+      <c r="A14" s="44"/>
       <c r="B14" s="45"/>
       <c r="C14" s="46"/>
       <c r="D14" s="47"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="22"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="44"/>
     </row>
     <row r="15" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
+      <c r="A15" s="44"/>
       <c r="B15" s="45"/>
       <c r="C15" s="46"/>
       <c r="D15" s="47"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="22"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="44"/>
     </row>
     <row r="16" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="22"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="44"/>
     </row>
     <row r="17" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="22"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="44"/>
     </row>
     <row r="18" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="22"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="44"/>
     </row>
     <row r="19" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="22"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="44"/>
     </row>
     <row r="20" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="22"/>
+      <c r="A20" s="44"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="21" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="24"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="52"/>
     </row>
     <row r="22" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
@@ -1021,59 +1028,59 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="52" t="s">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="52"/>
+      <c r="E23" s="22"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
     </row>
     <row r="24" spans="1:7" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
     </row>
     <row r="25" spans="1:7" s="4" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="53"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
     </row>
     <row r="26" spans="1:7" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="52" t="s">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="52"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="1:7" s="4" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
     </row>
     <row r="28" spans="1:7" s="4" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="6"/>
@@ -1091,24 +1098,24 @@
     <row r="30" spans="1:7" s="4" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:7" s="4" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:7" s="4" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="51"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:7" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
     </row>
     <row r="34" spans="1:7" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
@@ -1120,39 +1127,39 @@
       <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
     </row>
     <row r="36" spans="1:7" s="4" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A36" s="35" t="s">
+      <c r="A36" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
     </row>
     <row r="37" spans="1:7" s="4" customFormat="1" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="31"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
     </row>
     <row r="38" spans="1:7" s="4" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="29"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
@@ -1194,23 +1201,6 @@
     <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B13:D13"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D2:G2"/>
     <mergeCell ref="A8:C8"/>
@@ -1227,6 +1217,23 @@
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
